--- a/MainTop/18.09.2026 3гор/поставка/Москва_print_sorted.xlsx
+++ b/MainTop/18.09.2026 3гор/поставка/Москва_print_sorted.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
@@ -653,7 +653,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
@@ -765,7 +765,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
@@ -877,7 +877,7 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L11" s="1" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L14" s="1" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L15" s="1" t="n">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L16" s="1" t="n">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L17" s="1" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L18" s="1" t="n">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L19" s="1" t="n">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L20" s="1" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L21" s="1" t="n">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L22" s="1" t="n">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L23" s="1" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L24" s="1" t="n">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L25" s="1" t="n">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>18.09.2026 2гор</t>
+          <t>18.09.2026 3гор</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
